--- a/data/channel_priority.xlsx
+++ b/data/channel_priority.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EPGoal\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71949B30-A031-4F04-9859-E6D4C2DC7A61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60BC8670-7E39-47B6-B81D-7496C329E946}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Kanal-prioritering" sheetId="1" r:id="rId1"/>
@@ -2134,36 +2134,39 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>109</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>110</v>
       </c>
       <c r="C2" t="s">
-        <v>8</v>
+        <v>111</v>
       </c>
       <c r="D2">
-        <v>980</v>
+        <v>240</v>
       </c>
       <c r="E2">
-        <v>7.1</v>
+        <v>5</v>
+      </c>
+      <c r="F2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>78</v>
       </c>
       <c r="B3" t="s">
-        <v>10</v>
+        <v>79</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
+        <v>80</v>
       </c>
       <c r="D3">
-        <v>840</v>
+        <v>291</v>
       </c>
       <c r="E3">
-        <v>44.8</v>
+        <v>0</v>
       </c>
       <c r="F3" t="s">
         <v>12</v>
@@ -2171,104 +2174,119 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="C4" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="D4">
-        <v>657</v>
+        <v>370</v>
       </c>
       <c r="E4">
-        <v>9.1</v>
+        <v>0</v>
+      </c>
+      <c r="F4" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>75</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>76</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>77</v>
       </c>
       <c r="D5">
-        <v>657</v>
+        <v>297</v>
       </c>
       <c r="E5">
-        <v>48.1</v>
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="F5" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>18</v>
+        <v>106</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>107</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>108</v>
       </c>
       <c r="D6">
-        <v>512</v>
+        <v>258</v>
       </c>
       <c r="E6">
-        <v>1.6</v>
+        <v>0</v>
+      </c>
+      <c r="F6" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>21</v>
+        <v>60</v>
       </c>
       <c r="B7" t="s">
-        <v>22</v>
+        <v>61</v>
       </c>
       <c r="C7" t="s">
-        <v>23</v>
+        <v>62</v>
       </c>
       <c r="D7">
-        <v>456</v>
+        <v>330</v>
       </c>
       <c r="E7">
         <v>0</v>
+      </c>
+      <c r="F7" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="C8" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="D8">
-        <v>408</v>
+        <v>840</v>
       </c>
       <c r="E8">
-        <v>22.8</v>
+        <v>44.8</v>
+      </c>
+      <c r="F8" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B9" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C9" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D9">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E9">
-        <v>60.5</v>
+        <v>38.6</v>
       </c>
       <c r="F9" t="s">
         <v>12</v>
@@ -2276,19 +2294,19 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>30</v>
+        <v>69</v>
       </c>
       <c r="B10" t="s">
-        <v>31</v>
+        <v>70</v>
       </c>
       <c r="C10" t="s">
-        <v>32</v>
+        <v>71</v>
       </c>
       <c r="D10">
-        <v>394</v>
+        <v>306</v>
       </c>
       <c r="E10">
-        <v>38.6</v>
+        <v>35.299999999999997</v>
       </c>
       <c r="F10" t="s">
         <v>12</v>
@@ -2296,19 +2314,19 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>33</v>
+        <v>128</v>
       </c>
       <c r="B11" t="s">
-        <v>34</v>
+        <v>129</v>
       </c>
       <c r="C11" t="s">
-        <v>35</v>
+        <v>130</v>
       </c>
       <c r="D11">
-        <v>376</v>
+        <v>197</v>
       </c>
       <c r="E11">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="F11" t="s">
         <v>12</v>
@@ -2316,19 +2334,19 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="B12" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="C12" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="D12">
-        <v>372</v>
+        <v>346</v>
       </c>
       <c r="E12">
-        <v>40.1</v>
+        <v>1.2</v>
       </c>
       <c r="F12" t="s">
         <v>12</v>
@@ -2336,36 +2354,39 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>39</v>
+        <v>63</v>
       </c>
       <c r="B13" t="s">
-        <v>40</v>
+        <v>64</v>
       </c>
       <c r="C13" t="s">
-        <v>41</v>
+        <v>65</v>
       </c>
       <c r="D13">
-        <v>370</v>
+        <v>321</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>44.9</v>
+      </c>
+      <c r="F13" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B14" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C14" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D14">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="E14">
-        <v>56.2</v>
+        <v>19.399999999999999</v>
       </c>
       <c r="F14" t="s">
         <v>12</v>
@@ -2373,19 +2394,19 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>45</v>
+        <v>72</v>
       </c>
       <c r="B15" t="s">
-        <v>46</v>
+        <v>73</v>
       </c>
       <c r="C15" t="s">
-        <v>47</v>
+        <v>74</v>
       </c>
       <c r="D15">
-        <v>360</v>
+        <v>299</v>
       </c>
       <c r="E15">
-        <v>19.399999999999999</v>
+        <v>47.5</v>
       </c>
       <c r="F15" t="s">
         <v>12</v>
@@ -2393,19 +2414,19 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="B16" t="s">
-        <v>49</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>50</v>
+        <v>34</v>
+      </c>
+      <c r="C16" t="s">
+        <v>35</v>
       </c>
       <c r="D16">
-        <v>351</v>
+        <v>376</v>
       </c>
       <c r="E16">
-        <v>23.1</v>
+        <v>4.8</v>
       </c>
       <c r="F16" t="s">
         <v>12</v>
@@ -2413,19 +2434,19 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="B17" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="C17" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="D17">
-        <v>346</v>
+        <v>370</v>
       </c>
       <c r="E17">
-        <v>1.2</v>
+        <v>56.2</v>
       </c>
       <c r="F17" t="s">
         <v>12</v>
@@ -2433,19 +2454,19 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>54</v>
+        <v>27</v>
       </c>
       <c r="B18" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="C18" t="s">
-        <v>56</v>
+        <v>29</v>
       </c>
       <c r="D18">
-        <v>336</v>
+        <v>395</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>60.5</v>
       </c>
       <c r="F18" t="s">
         <v>12</v>
@@ -2453,36 +2474,39 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>57</v>
+        <v>147</v>
       </c>
       <c r="B19" t="s">
-        <v>58</v>
+        <v>148</v>
       </c>
       <c r="C19" t="s">
-        <v>59</v>
+        <v>149</v>
       </c>
       <c r="D19">
-        <v>334</v>
+        <v>177</v>
       </c>
       <c r="E19">
-        <v>9</v>
+        <v>0.6</v>
+      </c>
+      <c r="F19" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>60</v>
+        <v>180</v>
       </c>
       <c r="B20" t="s">
-        <v>61</v>
+        <v>181</v>
       </c>
       <c r="C20" t="s">
-        <v>62</v>
+        <v>182</v>
       </c>
       <c r="D20">
-        <v>330</v>
+        <v>149</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>65.099999999999994</v>
       </c>
       <c r="F20" t="s">
         <v>12</v>
@@ -2490,19 +2514,19 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>63</v>
+        <v>36</v>
       </c>
       <c r="B21" t="s">
-        <v>64</v>
+        <v>37</v>
       </c>
       <c r="C21" t="s">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="D21">
-        <v>321</v>
+        <v>372</v>
       </c>
       <c r="E21">
-        <v>44.9</v>
+        <v>40.1</v>
       </c>
       <c r="F21" t="s">
         <v>12</v>
@@ -2510,19 +2534,19 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="B22" t="s">
-        <v>67</v>
-      </c>
-      <c r="C22" t="s">
-        <v>68</v>
+        <v>49</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>50</v>
       </c>
       <c r="D22">
-        <v>307</v>
+        <v>351</v>
       </c>
       <c r="E22">
-        <v>24.4</v>
+        <v>23.1</v>
       </c>
       <c r="F22" t="s">
         <v>12</v>
@@ -2530,19 +2554,19 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>69</v>
+        <v>312</v>
       </c>
       <c r="B23" t="s">
-        <v>70</v>
+        <v>313</v>
       </c>
       <c r="C23" t="s">
+        <v>314</v>
+      </c>
+      <c r="D23">
         <v>71</v>
       </c>
-      <c r="D23">
-        <v>306</v>
-      </c>
       <c r="E23">
-        <v>35.299999999999997</v>
+        <v>60.6</v>
       </c>
       <c r="F23" t="s">
         <v>12</v>
@@ -2550,19 +2574,19 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="B24" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="C24" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="D24">
-        <v>299</v>
+        <v>336</v>
       </c>
       <c r="E24">
-        <v>47.5</v>
+        <v>0</v>
       </c>
       <c r="F24" t="s">
         <v>12</v>
@@ -2570,19 +2594,19 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="B25" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="C25" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="D25">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="E25">
-        <v>4.4000000000000004</v>
+        <v>24.4</v>
       </c>
       <c r="F25" t="s">
         <v>12</v>
@@ -2590,19 +2614,19 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>78</v>
+        <v>141</v>
       </c>
       <c r="B26" t="s">
-        <v>79</v>
+        <v>142</v>
       </c>
       <c r="C26" t="s">
-        <v>80</v>
+        <v>143</v>
       </c>
       <c r="D26">
-        <v>291</v>
+        <v>186</v>
       </c>
       <c r="E26">
-        <v>0</v>
+        <v>82.8</v>
       </c>
       <c r="F26" t="s">
         <v>12</v>
@@ -2610,695 +2634,683 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="B27" t="s">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="C27" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="D27">
-        <v>289</v>
+        <v>278</v>
       </c>
       <c r="E27">
-        <v>55</v>
+        <v>47.1</v>
+      </c>
+      <c r="F27" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="B28" t="s">
-        <v>85</v>
+        <v>104</v>
       </c>
       <c r="C28" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="D28">
-        <v>288</v>
+        <v>264</v>
       </c>
       <c r="E28">
-        <v>56.2</v>
+        <v>12.1</v>
+      </c>
+      <c r="F28" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>86</v>
+        <v>368</v>
       </c>
       <c r="B29" t="s">
-        <v>87</v>
+        <v>369</v>
       </c>
       <c r="C29" t="s">
-        <v>88</v>
+        <v>370</v>
       </c>
       <c r="D29">
-        <v>286</v>
+        <v>62</v>
       </c>
       <c r="E29">
-        <v>2.8</v>
+        <v>100</v>
+      </c>
+      <c r="F29" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>89</v>
+        <v>177</v>
       </c>
       <c r="B30" t="s">
-        <v>90</v>
+        <v>178</v>
       </c>
       <c r="C30" t="s">
-        <v>91</v>
+        <v>179</v>
       </c>
       <c r="D30">
-        <v>283</v>
+        <v>154</v>
       </c>
       <c r="E30">
-        <v>51.2</v>
+        <v>0</v>
+      </c>
+      <c r="F30" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>92</v>
+        <v>362</v>
       </c>
       <c r="B31" t="s">
-        <v>93</v>
+        <v>363</v>
       </c>
       <c r="C31" t="s">
-        <v>94</v>
+        <v>362</v>
       </c>
       <c r="D31">
-        <v>281</v>
+        <v>63</v>
       </c>
       <c r="E31">
-        <v>0</v>
+        <v>19</v>
+      </c>
+      <c r="F31" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>95</v>
+        <v>144</v>
       </c>
       <c r="B32" t="s">
-        <v>96</v>
+        <v>145</v>
       </c>
       <c r="C32" t="s">
-        <v>97</v>
+        <v>146</v>
       </c>
       <c r="D32">
-        <v>278</v>
+        <v>179</v>
       </c>
       <c r="E32">
-        <v>47.1</v>
+        <v>21.2</v>
       </c>
       <c r="F32" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>98</v>
+        <v>264</v>
       </c>
       <c r="B33" t="s">
-        <v>99</v>
+        <v>265</v>
       </c>
       <c r="C33" t="s">
-        <v>100</v>
+        <v>264</v>
       </c>
       <c r="D33">
-        <v>277</v>
+        <v>79</v>
       </c>
       <c r="E33">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>101</v>
+        <v>388</v>
       </c>
       <c r="B34" t="s">
-        <v>102</v>
+        <v>389</v>
       </c>
       <c r="C34" t="s">
-        <v>101</v>
+        <v>388</v>
       </c>
       <c r="D34">
-        <v>274</v>
+        <v>57</v>
       </c>
       <c r="E34">
-        <v>22.3</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
+        <v>169</v>
+      </c>
+      <c r="B35" t="s">
+        <v>170</v>
+      </c>
+      <c r="C35" t="s">
+        <v>171</v>
+      </c>
+      <c r="D35">
+        <v>155</v>
+      </c>
+      <c r="E35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>373</v>
+      </c>
+      <c r="B36" t="s">
+        <v>374</v>
+      </c>
+      <c r="C36" t="s">
+        <v>373</v>
+      </c>
+      <c r="D36">
+        <v>60</v>
+      </c>
+      <c r="E36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>225</v>
+      </c>
+      <c r="B37" t="s">
+        <v>226</v>
+      </c>
+      <c r="C37" t="s">
+        <v>225</v>
+      </c>
+      <c r="D37">
+        <v>113</v>
+      </c>
+      <c r="E37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>390</v>
+      </c>
+      <c r="B38" t="s">
+        <v>391</v>
+      </c>
+      <c r="C38" t="s">
+        <v>390</v>
+      </c>
+      <c r="D38">
+        <v>57</v>
+      </c>
+      <c r="E38">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>234</v>
+      </c>
+      <c r="B39" t="s">
+        <v>235</v>
+      </c>
+      <c r="C39" t="s">
+        <v>234</v>
+      </c>
+      <c r="D39">
         <v>103</v>
       </c>
-      <c r="B35" t="s">
-        <v>104</v>
-      </c>
-      <c r="C35" t="s">
-        <v>105</v>
-      </c>
-      <c r="D35">
-        <v>264</v>
-      </c>
-      <c r="E35">
-        <v>12.1</v>
-      </c>
-      <c r="F35" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>106</v>
-      </c>
-      <c r="B36" t="s">
+      <c r="E39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>436</v>
+      </c>
+      <c r="B40" t="s">
+        <v>437</v>
+      </c>
+      <c r="C40" t="s">
+        <v>436</v>
+      </c>
+      <c r="D40">
+        <v>48</v>
+      </c>
+      <c r="E40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>398</v>
+      </c>
+      <c r="B41" t="s">
+        <v>399</v>
+      </c>
+      <c r="C41" t="s">
+        <v>398</v>
+      </c>
+      <c r="D41">
+        <v>56</v>
+      </c>
+      <c r="E41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>232</v>
+      </c>
+      <c r="B42" t="s">
+        <v>233</v>
+      </c>
+      <c r="C42" t="s">
+        <v>232</v>
+      </c>
+      <c r="D42">
         <v>107</v>
       </c>
-      <c r="C36" t="s">
-        <v>108</v>
-      </c>
-      <c r="D36">
-        <v>258</v>
-      </c>
-      <c r="E36">
-        <v>0</v>
-      </c>
-      <c r="F36" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>109</v>
-      </c>
-      <c r="B37" t="s">
-        <v>110</v>
-      </c>
-      <c r="C37" t="s">
-        <v>111</v>
-      </c>
-      <c r="D37">
-        <v>240</v>
-      </c>
-      <c r="E37">
-        <v>5</v>
-      </c>
-      <c r="F37" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>112</v>
-      </c>
-      <c r="B38" t="s">
-        <v>113</v>
-      </c>
-      <c r="C38" t="s">
-        <v>114</v>
-      </c>
-      <c r="D38">
-        <v>227</v>
-      </c>
-      <c r="E38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>115</v>
-      </c>
-      <c r="B39" t="s">
-        <v>116</v>
-      </c>
-      <c r="C39" t="s">
-        <v>117</v>
-      </c>
-      <c r="D39">
-        <v>225</v>
-      </c>
-      <c r="E39">
-        <v>20.399999999999999</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>118</v>
-      </c>
-      <c r="B40" t="s">
-        <v>119</v>
-      </c>
-      <c r="C40" t="s">
-        <v>120</v>
-      </c>
-      <c r="D40">
-        <v>218</v>
-      </c>
-      <c r="E40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>121</v>
-      </c>
-      <c r="B41" t="s">
-        <v>122</v>
-      </c>
-      <c r="C41" t="s">
-        <v>123</v>
-      </c>
-      <c r="D41">
-        <v>215</v>
-      </c>
-      <c r="E41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>124</v>
-      </c>
-      <c r="B42" t="s">
-        <v>125</v>
-      </c>
-      <c r="C42" t="s">
-        <v>124</v>
-      </c>
-      <c r="D42">
-        <v>209</v>
-      </c>
       <c r="E42">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>126</v>
+        <v>210</v>
       </c>
       <c r="B43" t="s">
-        <v>127</v>
+        <v>211</v>
       </c>
       <c r="C43" t="s">
-        <v>126</v>
+        <v>210</v>
       </c>
       <c r="D43">
-        <v>202</v>
+        <v>131</v>
       </c>
       <c r="E43">
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>128</v>
+        <v>287</v>
       </c>
       <c r="B44" t="s">
-        <v>129</v>
+        <v>288</v>
       </c>
       <c r="C44" t="s">
-        <v>130</v>
+        <v>287</v>
       </c>
       <c r="D44">
-        <v>197</v>
+        <v>74</v>
       </c>
       <c r="E44">
-        <v>0</v>
-      </c>
-      <c r="F44" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>131</v>
+        <v>352</v>
       </c>
       <c r="B45" t="s">
-        <v>132</v>
+        <v>353</v>
       </c>
       <c r="C45" t="s">
-        <v>131</v>
+        <v>352</v>
       </c>
       <c r="D45">
-        <v>197</v>
+        <v>63</v>
       </c>
       <c r="E45">
-        <v>5.6</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
+        <v>86</v>
+      </c>
+      <c r="B46" t="s">
+        <v>87</v>
+      </c>
+      <c r="C46" t="s">
+        <v>88</v>
+      </c>
+      <c r="D46">
+        <v>286</v>
+      </c>
+      <c r="E46">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>477</v>
+      </c>
+      <c r="B47" t="s">
+        <v>478</v>
+      </c>
+      <c r="C47" t="s">
+        <v>477</v>
+      </c>
+      <c r="D47">
+        <v>35</v>
+      </c>
+      <c r="E47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>462</v>
+      </c>
+      <c r="B48" t="s">
+        <v>463</v>
+      </c>
+      <c r="C48" t="s">
+        <v>462</v>
+      </c>
+      <c r="D48">
+        <v>38</v>
+      </c>
+      <c r="E48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>371</v>
+      </c>
+      <c r="B49" t="s">
+        <v>372</v>
+      </c>
+      <c r="C49" t="s">
+        <v>371</v>
+      </c>
+      <c r="D49">
+        <v>61</v>
+      </c>
+      <c r="E49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>57</v>
+      </c>
+      <c r="B50" t="s">
+        <v>58</v>
+      </c>
+      <c r="C50" t="s">
+        <v>59</v>
+      </c>
+      <c r="D50">
+        <v>334</v>
+      </c>
+      <c r="E50">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>266</v>
+      </c>
+      <c r="B51" t="s">
+        <v>267</v>
+      </c>
+      <c r="C51" t="s">
+        <v>268</v>
+      </c>
+      <c r="D51">
+        <v>79</v>
+      </c>
+      <c r="E51">
+        <v>8.9</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>13</v>
+      </c>
+      <c r="B52" t="s">
+        <v>14</v>
+      </c>
+      <c r="C52" t="s">
+        <v>13</v>
+      </c>
+      <c r="D52">
+        <v>657</v>
+      </c>
+      <c r="E52">
+        <v>9.1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>6</v>
+      </c>
+      <c r="B53" t="s">
+        <v>7</v>
+      </c>
+      <c r="C53" t="s">
+        <v>8</v>
+      </c>
+      <c r="D53">
+        <v>980</v>
+      </c>
+      <c r="E53">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>241</v>
+      </c>
+      <c r="B54" t="s">
+        <v>242</v>
+      </c>
+      <c r="C54" t="s">
+        <v>241</v>
+      </c>
+      <c r="D54">
+        <v>96</v>
+      </c>
+      <c r="E54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
         <v>133</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B55" t="s">
         <v>134</v>
       </c>
-      <c r="C46" t="s">
+      <c r="C55" t="s">
         <v>135</v>
       </c>
-      <c r="D46">
+      <c r="D55">
         <v>192</v>
       </c>
-      <c r="E46">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>136</v>
-      </c>
-      <c r="B47" t="s">
-        <v>137</v>
-      </c>
-      <c r="C47" t="s">
-        <v>136</v>
-      </c>
-      <c r="D47">
-        <v>189</v>
-      </c>
-      <c r="E47">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
+      <c r="E55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>343</v>
+      </c>
+      <c r="B56" t="s">
+        <v>344</v>
+      </c>
+      <c r="C56" t="s">
+        <v>343</v>
+      </c>
+      <c r="D56">
+        <v>65</v>
+      </c>
+      <c r="E56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
         <v>138</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B57" t="s">
         <v>139</v>
       </c>
-      <c r="C48" t="s">
+      <c r="C57" t="s">
         <v>140</v>
       </c>
-      <c r="D48">
+      <c r="D57">
         <v>187</v>
       </c>
-      <c r="E48">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>141</v>
-      </c>
-      <c r="B49" t="s">
-        <v>142</v>
-      </c>
-      <c r="C49" t="s">
-        <v>143</v>
-      </c>
-      <c r="D49">
-        <v>186</v>
-      </c>
-      <c r="E49">
-        <v>82.8</v>
-      </c>
-      <c r="F49" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>144</v>
-      </c>
-      <c r="B50" t="s">
-        <v>145</v>
-      </c>
-      <c r="C50" t="s">
-        <v>146</v>
-      </c>
-      <c r="D50">
-        <v>179</v>
-      </c>
-      <c r="E50">
-        <v>21.2</v>
-      </c>
-      <c r="F50" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>147</v>
-      </c>
-      <c r="B51" t="s">
+      <c r="E57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>381</v>
+      </c>
+      <c r="B58" t="s">
+        <v>382</v>
+      </c>
+      <c r="C58" t="s">
+        <v>381</v>
+      </c>
+      <c r="D58">
+        <v>59</v>
+      </c>
+      <c r="E58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>175</v>
+      </c>
+      <c r="B59" t="s">
+        <v>176</v>
+      </c>
+      <c r="C59" t="s">
+        <v>175</v>
+      </c>
+      <c r="D59">
+        <v>154</v>
+      </c>
+      <c r="E59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>345</v>
+      </c>
+      <c r="B60" t="s">
+        <v>346</v>
+      </c>
+      <c r="C60" t="s">
+        <v>345</v>
+      </c>
+      <c r="D60">
+        <v>65</v>
+      </c>
+      <c r="E60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>408</v>
+      </c>
+      <c r="B61" t="s">
+        <v>409</v>
+      </c>
+      <c r="C61" t="s">
+        <v>408</v>
+      </c>
+      <c r="D61">
+        <v>54</v>
+      </c>
+      <c r="E61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>251</v>
+      </c>
+      <c r="B62" t="s">
+        <v>252</v>
+      </c>
+      <c r="C62" t="s">
+        <v>251</v>
+      </c>
+      <c r="D62">
+        <v>85</v>
+      </c>
+      <c r="E62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>183</v>
+      </c>
+      <c r="B63" t="s">
+        <v>184</v>
+      </c>
+      <c r="C63" t="s">
+        <v>183</v>
+      </c>
+      <c r="D63">
         <v>148</v>
       </c>
-      <c r="C51" t="s">
-        <v>149</v>
-      </c>
-      <c r="D51">
-        <v>177</v>
-      </c>
-      <c r="E51">
-        <v>0.6</v>
-      </c>
-      <c r="F51" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>150</v>
-      </c>
-      <c r="B52" t="s">
-        <v>151</v>
-      </c>
-      <c r="C52" t="s">
-        <v>152</v>
-      </c>
-      <c r="D52">
-        <v>174</v>
-      </c>
-      <c r="E52">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>153</v>
-      </c>
-      <c r="B53" t="s">
-        <v>154</v>
-      </c>
-      <c r="C53" t="s">
-        <v>153</v>
-      </c>
-      <c r="D53">
-        <v>174</v>
-      </c>
-      <c r="E53">
-        <v>35.1</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>155</v>
-      </c>
-      <c r="B54" t="s">
-        <v>156</v>
-      </c>
-      <c r="C54" t="s">
-        <v>155</v>
-      </c>
-      <c r="D54">
-        <v>173</v>
-      </c>
-      <c r="E54">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>157</v>
-      </c>
-      <c r="B55" t="s">
-        <v>158</v>
-      </c>
-      <c r="C55" t="s">
-        <v>157</v>
-      </c>
-      <c r="D55">
-        <v>171</v>
-      </c>
-      <c r="E55">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>159</v>
-      </c>
-      <c r="B56" t="s">
-        <v>160</v>
-      </c>
-      <c r="C56" t="s">
-        <v>161</v>
-      </c>
-      <c r="D56">
-        <v>168</v>
-      </c>
-      <c r="E56">
-        <v>9.5</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>162</v>
-      </c>
-      <c r="B57" t="s">
-        <v>163</v>
-      </c>
-      <c r="C57" t="s">
-        <v>162</v>
-      </c>
-      <c r="D57">
-        <v>164</v>
-      </c>
-      <c r="E57">
-        <v>7.9</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>164</v>
-      </c>
-      <c r="B58" t="s">
-        <v>165</v>
-      </c>
-      <c r="C58" t="s">
-        <v>166</v>
-      </c>
-      <c r="D58">
-        <v>163</v>
-      </c>
-      <c r="E58">
-        <v>6.1</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>167</v>
-      </c>
-      <c r="B59" t="s">
-        <v>168</v>
-      </c>
-      <c r="C59" t="s">
-        <v>167</v>
-      </c>
-      <c r="D59">
-        <v>161</v>
-      </c>
-      <c r="E59">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>169</v>
-      </c>
-      <c r="B60" t="s">
-        <v>170</v>
-      </c>
-      <c r="C60" t="s">
-        <v>171</v>
-      </c>
-      <c r="D60">
-        <v>155</v>
-      </c>
-      <c r="E60">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>172</v>
-      </c>
-      <c r="B61" t="s">
-        <v>173</v>
-      </c>
-      <c r="C61" t="s">
-        <v>174</v>
-      </c>
-      <c r="D61">
-        <v>155</v>
-      </c>
-      <c r="E61">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>175</v>
-      </c>
-      <c r="B62" t="s">
-        <v>176</v>
-      </c>
-      <c r="C62" t="s">
-        <v>175</v>
-      </c>
-      <c r="D62">
-        <v>154</v>
-      </c>
-      <c r="E62">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>177</v>
-      </c>
-      <c r="B63" t="s">
-        <v>178</v>
-      </c>
-      <c r="C63" t="s">
-        <v>179</v>
-      </c>
-      <c r="D63">
-        <v>154</v>
-      </c>
       <c r="E63">
-        <v>0</v>
-      </c>
-      <c r="F63" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+        <v>35.799999999999997</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>180</v>
+        <v>84</v>
       </c>
       <c r="B64" t="s">
-        <v>181</v>
+        <v>85</v>
       </c>
       <c r="C64" t="s">
-        <v>182</v>
+        <v>84</v>
       </c>
       <c r="D64">
-        <v>149</v>
+        <v>288</v>
       </c>
       <c r="E64">
-        <v>65.099999999999994</v>
-      </c>
-      <c r="F64" t="s">
-        <v>12</v>
+        <v>56.2</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>183</v>
+        <v>81</v>
       </c>
       <c r="B65" t="s">
-        <v>184</v>
+        <v>82</v>
       </c>
       <c r="C65" t="s">
-        <v>183</v>
+        <v>83</v>
       </c>
       <c r="D65">
-        <v>148</v>
+        <v>289</v>
       </c>
       <c r="E65">
-        <v>35.799999999999997</v>
+        <v>55</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
@@ -3320,50 +3332,50 @@
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>188</v>
+        <v>392</v>
       </c>
       <c r="B67" t="s">
-        <v>189</v>
+        <v>393</v>
       </c>
       <c r="C67" t="s">
-        <v>188</v>
+        <v>392</v>
       </c>
       <c r="D67">
-        <v>144</v>
+        <v>57</v>
       </c>
       <c r="E67">
-        <v>9.6999999999999993</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>190</v>
+        <v>18</v>
       </c>
       <c r="B68" t="s">
-        <v>191</v>
+        <v>19</v>
       </c>
       <c r="C68" t="s">
-        <v>190</v>
+        <v>20</v>
       </c>
       <c r="D68">
-        <v>141</v>
+        <v>512</v>
       </c>
       <c r="E68">
-        <v>0</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>192</v>
+        <v>136</v>
       </c>
       <c r="B69" t="s">
-        <v>193</v>
+        <v>137</v>
       </c>
       <c r="C69" t="s">
-        <v>192</v>
+        <v>136</v>
       </c>
       <c r="D69">
-        <v>139</v>
+        <v>189</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -3371,16 +3383,16 @@
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B70" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C70" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="D70">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -3388,50 +3400,50 @@
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>197</v>
+        <v>400</v>
       </c>
       <c r="B71" t="s">
-        <v>198</v>
+        <v>401</v>
       </c>
       <c r="C71" t="s">
-        <v>197</v>
+        <v>400</v>
       </c>
       <c r="D71">
-        <v>138</v>
+        <v>56</v>
       </c>
       <c r="E71">
-        <v>23.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>199</v>
+        <v>167</v>
       </c>
       <c r="B72" t="s">
-        <v>200</v>
+        <v>168</v>
       </c>
       <c r="C72" t="s">
-        <v>199</v>
+        <v>167</v>
       </c>
       <c r="D72">
-        <v>136</v>
+        <v>161</v>
       </c>
       <c r="E72">
-        <v>3.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>201</v>
+        <v>479</v>
       </c>
       <c r="B73" t="s">
-        <v>202</v>
+        <v>480</v>
       </c>
       <c r="C73" t="s">
-        <v>203</v>
+        <v>479</v>
       </c>
       <c r="D73">
-        <v>135</v>
+        <v>35</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -3439,67 +3451,67 @@
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>204</v>
+        <v>150</v>
       </c>
       <c r="B74" t="s">
-        <v>205</v>
+        <v>151</v>
       </c>
       <c r="C74" t="s">
-        <v>204</v>
+        <v>152</v>
       </c>
       <c r="D74">
-        <v>132</v>
+        <v>174</v>
       </c>
       <c r="E74">
-        <v>37.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>206</v>
+        <v>121</v>
       </c>
       <c r="B75" t="s">
-        <v>207</v>
+        <v>122</v>
       </c>
       <c r="C75" t="s">
-        <v>206</v>
+        <v>123</v>
       </c>
       <c r="D75">
-        <v>132</v>
+        <v>215</v>
       </c>
       <c r="E75">
-        <v>1.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>208</v>
+        <v>410</v>
       </c>
       <c r="B76" t="s">
-        <v>209</v>
+        <v>411</v>
       </c>
       <c r="C76" t="s">
-        <v>208</v>
+        <v>410</v>
       </c>
       <c r="D76">
-        <v>132</v>
+        <v>54</v>
       </c>
       <c r="E76">
-        <v>37.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>210</v>
+        <v>492</v>
       </c>
       <c r="B77" t="s">
-        <v>211</v>
+        <v>493</v>
       </c>
       <c r="C77" t="s">
-        <v>210</v>
+        <v>494</v>
       </c>
       <c r="D77">
-        <v>131</v>
+        <v>32</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -3507,101 +3519,101 @@
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>212</v>
+        <v>124</v>
       </c>
       <c r="B78" t="s">
-        <v>213</v>
+        <v>125</v>
       </c>
       <c r="C78" t="s">
-        <v>212</v>
+        <v>124</v>
       </c>
       <c r="D78">
-        <v>126</v>
+        <v>209</v>
       </c>
       <c r="E78">
-        <v>39.700000000000003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>214</v>
+        <v>230</v>
       </c>
       <c r="B79" t="s">
-        <v>215</v>
+        <v>231</v>
       </c>
       <c r="C79" t="s">
-        <v>214</v>
+        <v>230</v>
       </c>
       <c r="D79">
-        <v>124</v>
+        <v>109</v>
       </c>
       <c r="E79">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>216</v>
+        <v>350</v>
       </c>
       <c r="B80" t="s">
-        <v>217</v>
+        <v>351</v>
       </c>
       <c r="C80" t="s">
-        <v>216</v>
+        <v>350</v>
       </c>
       <c r="D80">
-        <v>124</v>
+        <v>64</v>
       </c>
       <c r="E80">
-        <v>40.299999999999997</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>218</v>
+        <v>317</v>
       </c>
       <c r="B81" t="s">
-        <v>219</v>
+        <v>318</v>
       </c>
       <c r="C81" t="s">
-        <v>218</v>
+        <v>317</v>
       </c>
       <c r="D81">
-        <v>120</v>
+        <v>69</v>
       </c>
       <c r="E81">
-        <v>1.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>220</v>
+        <v>321</v>
       </c>
       <c r="B82" t="s">
-        <v>221</v>
+        <v>322</v>
       </c>
       <c r="C82" t="s">
-        <v>222</v>
+        <v>321</v>
       </c>
       <c r="D82">
-        <v>117</v>
+        <v>69</v>
       </c>
       <c r="E82">
-        <v>4.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>223</v>
+        <v>308</v>
       </c>
       <c r="B83" t="s">
-        <v>224</v>
+        <v>309</v>
       </c>
       <c r="C83" t="s">
-        <v>223</v>
+        <v>308</v>
       </c>
       <c r="D83">
-        <v>116</v>
+        <v>71</v>
       </c>
       <c r="E83">
         <v>0</v>
@@ -3609,16 +3621,16 @@
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>225</v>
+        <v>194</v>
       </c>
       <c r="B84" t="s">
-        <v>226</v>
+        <v>195</v>
       </c>
       <c r="C84" t="s">
-        <v>225</v>
+        <v>196</v>
       </c>
       <c r="D84">
-        <v>113</v>
+        <v>138</v>
       </c>
       <c r="E84">
         <v>0</v>
@@ -3626,33 +3638,33 @@
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>227</v>
+        <v>319</v>
       </c>
       <c r="B85" t="s">
-        <v>228</v>
+        <v>320</v>
       </c>
       <c r="C85" t="s">
-        <v>229</v>
+        <v>319</v>
       </c>
       <c r="D85">
-        <v>113</v>
+        <v>69</v>
       </c>
       <c r="E85">
-        <v>3.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>230</v>
+        <v>464</v>
       </c>
       <c r="B86" t="s">
-        <v>231</v>
+        <v>465</v>
       </c>
       <c r="C86" t="s">
-        <v>230</v>
+        <v>464</v>
       </c>
       <c r="D86">
-        <v>109</v>
+        <v>38</v>
       </c>
       <c r="E86">
         <v>0</v>
@@ -3660,33 +3672,33 @@
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>232</v>
+        <v>454</v>
       </c>
       <c r="B87" t="s">
-        <v>233</v>
+        <v>455</v>
       </c>
       <c r="C87" t="s">
-        <v>232</v>
+        <v>454</v>
       </c>
       <c r="D87">
-        <v>107</v>
+        <v>41</v>
       </c>
       <c r="E87">
-        <v>3.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>234</v>
+        <v>446</v>
       </c>
       <c r="B88" t="s">
-        <v>235</v>
+        <v>447</v>
       </c>
       <c r="C88" t="s">
-        <v>234</v>
+        <v>446</v>
       </c>
       <c r="D88">
-        <v>103</v>
+        <v>46</v>
       </c>
       <c r="E88">
         <v>0</v>
@@ -3694,33 +3706,33 @@
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>236</v>
+        <v>426</v>
       </c>
       <c r="B89" t="s">
-        <v>237</v>
+        <v>427</v>
       </c>
       <c r="C89" t="s">
-        <v>236</v>
+        <v>426</v>
       </c>
       <c r="D89">
-        <v>99</v>
+        <v>51</v>
       </c>
       <c r="E89">
-        <v>6.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>238</v>
+        <v>499</v>
       </c>
       <c r="B90" t="s">
-        <v>239</v>
+        <v>500</v>
       </c>
       <c r="C90" t="s">
-        <v>240</v>
+        <v>499</v>
       </c>
       <c r="D90">
-        <v>99</v>
+        <v>27</v>
       </c>
       <c r="E90">
         <v>0</v>
@@ -3728,50 +3740,50 @@
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>241</v>
+        <v>204</v>
       </c>
       <c r="B91" t="s">
-        <v>242</v>
+        <v>205</v>
       </c>
       <c r="C91" t="s">
-        <v>241</v>
+        <v>204</v>
       </c>
       <c r="D91">
-        <v>96</v>
+        <v>132</v>
       </c>
       <c r="E91">
-        <v>0</v>
+        <v>37.9</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>243</v>
+        <v>416</v>
       </c>
       <c r="B92" t="s">
-        <v>244</v>
+        <v>417</v>
       </c>
       <c r="C92" t="s">
-        <v>243</v>
+        <v>416</v>
       </c>
       <c r="D92">
-        <v>93</v>
+        <v>53</v>
       </c>
       <c r="E92">
-        <v>0</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B93" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C93" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D93">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E93">
         <v>0</v>
@@ -3779,16 +3791,16 @@
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>247</v>
+        <v>458</v>
       </c>
       <c r="B94" t="s">
-        <v>248</v>
+        <v>459</v>
       </c>
       <c r="C94" t="s">
-        <v>247</v>
+        <v>458</v>
       </c>
       <c r="D94">
-        <v>86</v>
+        <v>39</v>
       </c>
       <c r="E94">
         <v>0</v>
@@ -3796,16 +3808,16 @@
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>249</v>
+        <v>448</v>
       </c>
       <c r="B95" t="s">
-        <v>250</v>
+        <v>449</v>
       </c>
       <c r="C95" t="s">
-        <v>249</v>
+        <v>448</v>
       </c>
       <c r="D95">
-        <v>86</v>
+        <v>46</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -3813,16 +3825,16 @@
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="B96" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="C96" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="D96">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="E96">
         <v>0</v>
@@ -3830,16 +3842,16 @@
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="B97" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="C97" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="D97">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E97">
         <v>0</v>
@@ -3847,33 +3859,33 @@
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>255</v>
+        <v>394</v>
       </c>
       <c r="B98" t="s">
-        <v>256</v>
+        <v>395</v>
       </c>
       <c r="C98" t="s">
-        <v>255</v>
+        <v>394</v>
       </c>
       <c r="D98">
-        <v>81</v>
+        <v>57</v>
       </c>
       <c r="E98">
-        <v>4.9000000000000004</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>257</v>
+        <v>21</v>
       </c>
       <c r="B99" t="s">
-        <v>258</v>
+        <v>22</v>
       </c>
       <c r="C99" t="s">
-        <v>257</v>
+        <v>23</v>
       </c>
       <c r="D99">
-        <v>80</v>
+        <v>456</v>
       </c>
       <c r="E99">
         <v>0</v>
@@ -3881,1388 +3893,1376 @@
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>259</v>
+        <v>420</v>
       </c>
       <c r="B100" t="s">
-        <v>260</v>
+        <v>421</v>
       </c>
       <c r="C100" t="s">
-        <v>259</v>
+        <v>420</v>
       </c>
       <c r="D100">
-        <v>80</v>
+        <v>52</v>
       </c>
       <c r="E100">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>261</v>
+        <v>289</v>
       </c>
       <c r="B101" t="s">
-        <v>262</v>
+        <v>290</v>
       </c>
       <c r="C101" t="s">
-        <v>263</v>
+        <v>289</v>
       </c>
       <c r="D101">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="E101">
-        <v>7.5</v>
+        <v>16.2</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>264</v>
+        <v>291</v>
       </c>
       <c r="B102" t="s">
-        <v>265</v>
+        <v>292</v>
       </c>
       <c r="C102" t="s">
-        <v>264</v>
+        <v>291</v>
       </c>
       <c r="D102">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="E102">
-        <v>0</v>
+        <v>25.7</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>266</v>
+        <v>245</v>
       </c>
       <c r="B103" t="s">
-        <v>267</v>
+        <v>246</v>
       </c>
       <c r="C103" t="s">
-        <v>268</v>
+        <v>245</v>
       </c>
       <c r="D103">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="E103">
-        <v>8.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>269</v>
+        <v>157</v>
       </c>
       <c r="B104" t="s">
-        <v>270</v>
+        <v>158</v>
       </c>
       <c r="C104" t="s">
-        <v>269</v>
+        <v>157</v>
       </c>
       <c r="D104">
-        <v>79</v>
+        <v>171</v>
       </c>
       <c r="E104">
-        <v>8.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>271</v>
+        <v>190</v>
       </c>
       <c r="B105" t="s">
-        <v>272</v>
+        <v>191</v>
       </c>
       <c r="C105" t="s">
-        <v>271</v>
+        <v>190</v>
       </c>
       <c r="D105">
-        <v>79</v>
+        <v>141</v>
       </c>
       <c r="E105">
-        <v>3.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>273</v>
+        <v>24</v>
       </c>
       <c r="B106" t="s">
-        <v>274</v>
+        <v>25</v>
       </c>
       <c r="C106" t="s">
-        <v>275</v>
+        <v>26</v>
       </c>
       <c r="D106">
-        <v>78</v>
+        <v>408</v>
       </c>
       <c r="E106">
-        <v>0</v>
+        <v>22.8</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>276</v>
+        <v>101</v>
       </c>
       <c r="B107" t="s">
-        <v>277</v>
+        <v>102</v>
       </c>
       <c r="C107" t="s">
-        <v>276</v>
+        <v>101</v>
       </c>
       <c r="D107">
-        <v>77</v>
+        <v>274</v>
       </c>
       <c r="E107">
-        <v>0</v>
+        <v>22.3</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>278</v>
+        <v>197</v>
       </c>
       <c r="B108" t="s">
-        <v>279</v>
+        <v>198</v>
       </c>
       <c r="C108" t="s">
-        <v>278</v>
+        <v>197</v>
       </c>
       <c r="D108">
-        <v>76</v>
+        <v>138</v>
       </c>
       <c r="E108">
-        <v>0</v>
+        <v>23.2</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>280</v>
+        <v>15</v>
       </c>
       <c r="B109" t="s">
-        <v>281</v>
+        <v>16</v>
       </c>
       <c r="C109" t="s">
-        <v>280</v>
+        <v>17</v>
       </c>
       <c r="D109">
-        <v>76</v>
+        <v>657</v>
       </c>
       <c r="E109">
-        <v>2.6</v>
+        <v>48.1</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>282</v>
+        <v>89</v>
       </c>
       <c r="B110" t="s">
+        <v>90</v>
+      </c>
+      <c r="C110" t="s">
+        <v>91</v>
+      </c>
+      <c r="D110">
         <v>283</v>
       </c>
-      <c r="C110" t="s">
-        <v>282</v>
-      </c>
-      <c r="D110">
-        <v>75</v>
-      </c>
       <c r="E110">
-        <v>36</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>284</v>
+        <v>520</v>
       </c>
       <c r="B111" t="s">
-        <v>285</v>
+        <v>521</v>
       </c>
       <c r="C111" t="s">
-        <v>286</v>
+        <v>520</v>
       </c>
       <c r="D111">
-        <v>75</v>
+        <v>23</v>
       </c>
       <c r="E111">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>287</v>
+        <v>131</v>
       </c>
       <c r="B112" t="s">
-        <v>288</v>
+        <v>132</v>
       </c>
       <c r="C112" t="s">
-        <v>287</v>
+        <v>131</v>
       </c>
       <c r="D112">
+        <v>197</v>
+      </c>
+      <c r="E112">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>406</v>
+      </c>
+      <c r="B113" t="s">
+        <v>407</v>
+      </c>
+      <c r="C113" t="s">
+        <v>406</v>
+      </c>
+      <c r="D113">
+        <v>55</v>
+      </c>
+      <c r="E113">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>172</v>
+      </c>
+      <c r="B114" t="s">
+        <v>173</v>
+      </c>
+      <c r="C114" t="s">
+        <v>174</v>
+      </c>
+      <c r="D114">
+        <v>155</v>
+      </c>
+      <c r="E114">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>236</v>
+      </c>
+      <c r="B115" t="s">
+        <v>237</v>
+      </c>
+      <c r="C115" t="s">
+        <v>236</v>
+      </c>
+      <c r="D115">
+        <v>99</v>
+      </c>
+      <c r="E115">
+        <v>6.1</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>98</v>
+      </c>
+      <c r="B116" t="s">
+        <v>99</v>
+      </c>
+      <c r="C116" t="s">
+        <v>100</v>
+      </c>
+      <c r="D116">
+        <v>277</v>
+      </c>
+      <c r="E116">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>199</v>
+      </c>
+      <c r="B117" t="s">
+        <v>200</v>
+      </c>
+      <c r="C117" t="s">
+        <v>199</v>
+      </c>
+      <c r="D117">
+        <v>136</v>
+      </c>
+      <c r="E117">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>214</v>
+      </c>
+      <c r="B118" t="s">
+        <v>215</v>
+      </c>
+      <c r="C118" t="s">
+        <v>214</v>
+      </c>
+      <c r="D118">
+        <v>124</v>
+      </c>
+      <c r="E118">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>153</v>
+      </c>
+      <c r="B119" t="s">
+        <v>154</v>
+      </c>
+      <c r="C119" t="s">
+        <v>153</v>
+      </c>
+      <c r="D119">
+        <v>174</v>
+      </c>
+      <c r="E119">
+        <v>35.1</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>282</v>
+      </c>
+      <c r="B120" t="s">
+        <v>283</v>
+      </c>
+      <c r="C120" t="s">
+        <v>282</v>
+      </c>
+      <c r="D120">
+        <v>75</v>
+      </c>
+      <c r="E120">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>278</v>
+      </c>
+      <c r="B121" t="s">
+        <v>279</v>
+      </c>
+      <c r="C121" t="s">
+        <v>278</v>
+      </c>
+      <c r="D121">
+        <v>76</v>
+      </c>
+      <c r="E121">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>535</v>
+      </c>
+      <c r="B122" t="s">
+        <v>536</v>
+      </c>
+      <c r="C122" t="s">
+        <v>535</v>
+      </c>
+      <c r="D122">
+        <v>13</v>
+      </c>
+      <c r="E122">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>206</v>
+      </c>
+      <c r="B123" t="s">
+        <v>207</v>
+      </c>
+      <c r="C123" t="s">
+        <v>206</v>
+      </c>
+      <c r="D123">
+        <v>132</v>
+      </c>
+      <c r="E123">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>483</v>
+      </c>
+      <c r="B124" t="s">
+        <v>484</v>
+      </c>
+      <c r="C124" t="s">
+        <v>483</v>
+      </c>
+      <c r="D124">
+        <v>33</v>
+      </c>
+      <c r="E124">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>310</v>
+      </c>
+      <c r="B125" t="s">
+        <v>311</v>
+      </c>
+      <c r="C125" t="s">
+        <v>310</v>
+      </c>
+      <c r="D125">
+        <v>71</v>
+      </c>
+      <c r="E125">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>298</v>
+      </c>
+      <c r="B126" t="s">
+        <v>299</v>
+      </c>
+      <c r="C126" t="s">
+        <v>298</v>
+      </c>
+      <c r="D126">
+        <v>73</v>
+      </c>
+      <c r="E126">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>529</v>
+      </c>
+      <c r="B127" t="s">
+        <v>530</v>
+      </c>
+      <c r="C127" t="s">
+        <v>529</v>
+      </c>
+      <c r="D127">
+        <v>14</v>
+      </c>
+      <c r="E127">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>386</v>
+      </c>
+      <c r="B128" t="s">
+        <v>387</v>
+      </c>
+      <c r="C128" t="s">
+        <v>386</v>
+      </c>
+      <c r="D128">
+        <v>58</v>
+      </c>
+      <c r="E128">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>450</v>
+      </c>
+      <c r="B129" t="s">
+        <v>451</v>
+      </c>
+      <c r="C129" t="s">
+        <v>450</v>
+      </c>
+      <c r="D129">
+        <v>45</v>
+      </c>
+      <c r="E129">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>412</v>
+      </c>
+      <c r="B130" t="s">
+        <v>413</v>
+      </c>
+      <c r="C130" t="s">
+        <v>412</v>
+      </c>
+      <c r="D130">
+        <v>54</v>
+      </c>
+      <c r="E130">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>460</v>
+      </c>
+      <c r="B131" t="s">
+        <v>461</v>
+      </c>
+      <c r="C131" t="s">
+        <v>460</v>
+      </c>
+      <c r="D131">
+        <v>39</v>
+      </c>
+      <c r="E131">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>485</v>
+      </c>
+      <c r="B132" t="s">
+        <v>486</v>
+      </c>
+      <c r="C132" t="s">
+        <v>487</v>
+      </c>
+      <c r="D132">
+        <v>33</v>
+      </c>
+      <c r="E132">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>495</v>
+      </c>
+      <c r="B133" t="s">
+        <v>496</v>
+      </c>
+      <c r="C133" t="s">
+        <v>495</v>
+      </c>
+      <c r="D133">
+        <v>31</v>
+      </c>
+      <c r="E133">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>383</v>
+      </c>
+      <c r="B134" t="s">
+        <v>384</v>
+      </c>
+      <c r="C134" t="s">
+        <v>385</v>
+      </c>
+      <c r="D134">
+        <v>59</v>
+      </c>
+      <c r="E134">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>253</v>
+      </c>
+      <c r="B135" t="s">
+        <v>254</v>
+      </c>
+      <c r="C135" t="s">
+        <v>253</v>
+      </c>
+      <c r="D135">
+        <v>84</v>
+      </c>
+      <c r="E135">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>257</v>
+      </c>
+      <c r="B136" t="s">
+        <v>258</v>
+      </c>
+      <c r="C136" t="s">
+        <v>257</v>
+      </c>
+      <c r="D136">
+        <v>80</v>
+      </c>
+      <c r="E136">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>164</v>
+      </c>
+      <c r="B137" t="s">
+        <v>165</v>
+      </c>
+      <c r="C137" t="s">
+        <v>166</v>
+      </c>
+      <c r="D137">
+        <v>163</v>
+      </c>
+      <c r="E137">
+        <v>6.1</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>227</v>
+      </c>
+      <c r="B138" t="s">
+        <v>228</v>
+      </c>
+      <c r="C138" t="s">
+        <v>229</v>
+      </c>
+      <c r="D138">
+        <v>113</v>
+      </c>
+      <c r="E138">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>330</v>
+      </c>
+      <c r="B139" t="s">
+        <v>331</v>
+      </c>
+      <c r="C139" t="s">
+        <v>332</v>
+      </c>
+      <c r="D139">
+        <v>66</v>
+      </c>
+      <c r="E139">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>315</v>
+      </c>
+      <c r="B140" t="s">
+        <v>316</v>
+      </c>
+      <c r="C140" t="s">
+        <v>315</v>
+      </c>
+      <c r="D140">
+        <v>70</v>
+      </c>
+      <c r="E140">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>259</v>
+      </c>
+      <c r="B141" t="s">
+        <v>260</v>
+      </c>
+      <c r="C141" t="s">
+        <v>259</v>
+      </c>
+      <c r="D141">
+        <v>80</v>
+      </c>
+      <c r="E141">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>531</v>
+      </c>
+      <c r="B142" t="s">
+        <v>532</v>
+      </c>
+      <c r="C142" t="s">
+        <v>531</v>
+      </c>
+      <c r="D142">
+        <v>14</v>
+      </c>
+      <c r="E142">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>188</v>
+      </c>
+      <c r="B143" t="s">
+        <v>189</v>
+      </c>
+      <c r="C143" t="s">
+        <v>188</v>
+      </c>
+      <c r="D143">
+        <v>144</v>
+      </c>
+      <c r="E143">
+        <v>9.6999999999999993</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>402</v>
+      </c>
+      <c r="B144" t="s">
+        <v>403</v>
+      </c>
+      <c r="C144" t="s">
+        <v>402</v>
+      </c>
+      <c r="D144">
+        <v>56</v>
+      </c>
+      <c r="E144">
+        <v>10.7</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>159</v>
+      </c>
+      <c r="B145" t="s">
+        <v>160</v>
+      </c>
+      <c r="C145" t="s">
+        <v>161</v>
+      </c>
+      <c r="D145">
+        <v>168</v>
+      </c>
+      <c r="E145">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>475</v>
+      </c>
+      <c r="B146" t="s">
+        <v>476</v>
+      </c>
+      <c r="C146" t="s">
+        <v>475</v>
+      </c>
+      <c r="D146">
+        <v>36</v>
+      </c>
+      <c r="E146">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>220</v>
+      </c>
+      <c r="B147" t="s">
+        <v>221</v>
+      </c>
+      <c r="C147" t="s">
+        <v>222</v>
+      </c>
+      <c r="D147">
+        <v>117</v>
+      </c>
+      <c r="E147">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>438</v>
+      </c>
+      <c r="B148" t="s">
+        <v>439</v>
+      </c>
+      <c r="C148" t="s">
+        <v>438</v>
+      </c>
+      <c r="D148">
+        <v>48</v>
+      </c>
+      <c r="E148">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>92</v>
+      </c>
+      <c r="B149" t="s">
+        <v>93</v>
+      </c>
+      <c r="C149" t="s">
+        <v>94</v>
+      </c>
+      <c r="D149">
+        <v>281</v>
+      </c>
+      <c r="E149">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>422</v>
+      </c>
+      <c r="B150" t="s">
+        <v>423</v>
+      </c>
+      <c r="C150" t="s">
+        <v>422</v>
+      </c>
+      <c r="D150">
+        <v>52</v>
+      </c>
+      <c r="E150">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>440</v>
+      </c>
+      <c r="B151" t="s">
+        <v>441</v>
+      </c>
+      <c r="C151" t="s">
+        <v>440</v>
+      </c>
+      <c r="D151">
+        <v>48</v>
+      </c>
+      <c r="E151">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>255</v>
+      </c>
+      <c r="B152" t="s">
+        <v>256</v>
+      </c>
+      <c r="C152" t="s">
+        <v>255</v>
+      </c>
+      <c r="D152">
+        <v>81</v>
+      </c>
+      <c r="E152">
+        <v>4.9000000000000004</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>336</v>
+      </c>
+      <c r="B153" t="s">
+        <v>337</v>
+      </c>
+      <c r="C153" t="s">
+        <v>336</v>
+      </c>
+      <c r="D153">
+        <v>66</v>
+      </c>
+      <c r="E153">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>162</v>
+      </c>
+      <c r="B154" t="s">
+        <v>163</v>
+      </c>
+      <c r="C154" t="s">
+        <v>162</v>
+      </c>
+      <c r="D154">
+        <v>164</v>
+      </c>
+      <c r="E154">
+        <v>7.9</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>155</v>
+      </c>
+      <c r="B155" t="s">
+        <v>156</v>
+      </c>
+      <c r="C155" t="s">
+        <v>155</v>
+      </c>
+      <c r="D155">
+        <v>173</v>
+      </c>
+      <c r="E155">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>501</v>
+      </c>
+      <c r="B156" t="s">
+        <v>502</v>
+      </c>
+      <c r="C156" t="s">
+        <v>501</v>
+      </c>
+      <c r="D156">
+        <v>27</v>
+      </c>
+      <c r="E156">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>497</v>
+      </c>
+      <c r="B157" t="s">
+        <v>498</v>
+      </c>
+      <c r="C157" t="s">
+        <v>497</v>
+      </c>
+      <c r="D157">
+        <v>29</v>
+      </c>
+      <c r="E157">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>543</v>
+      </c>
+      <c r="B158" t="s">
+        <v>544</v>
+      </c>
+      <c r="C158" t="s">
+        <v>543</v>
+      </c>
+      <c r="D158">
+        <v>10</v>
+      </c>
+      <c r="E158">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>306</v>
+      </c>
+      <c r="B159" t="s">
+        <v>307</v>
+      </c>
+      <c r="C159" t="s">
+        <v>306</v>
+      </c>
+      <c r="D159">
+        <v>72</v>
+      </c>
+      <c r="E159">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>293</v>
+      </c>
+      <c r="B160" t="s">
+        <v>294</v>
+      </c>
+      <c r="C160" t="s">
+        <v>293</v>
+      </c>
+      <c r="D160">
         <v>74</v>
       </c>
-      <c r="E112">
-        <v>2.7</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A113" t="s">
-        <v>289</v>
-      </c>
-      <c r="B113" t="s">
-        <v>290</v>
-      </c>
-      <c r="C113" t="s">
-        <v>289</v>
-      </c>
-      <c r="D113">
-        <v>74</v>
-      </c>
-      <c r="E113">
-        <v>16.2</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A114" t="s">
-        <v>291</v>
-      </c>
-      <c r="B114" t="s">
-        <v>292</v>
-      </c>
-      <c r="C114" t="s">
-        <v>291</v>
-      </c>
-      <c r="D114">
-        <v>74</v>
-      </c>
-      <c r="E114">
-        <v>25.7</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A115" t="s">
-        <v>293</v>
-      </c>
-      <c r="B115" t="s">
-        <v>294</v>
-      </c>
-      <c r="C115" t="s">
-        <v>293</v>
-      </c>
-      <c r="D115">
-        <v>74</v>
-      </c>
-      <c r="E115">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A116" t="s">
-        <v>295</v>
-      </c>
-      <c r="B116" t="s">
-        <v>296</v>
-      </c>
-      <c r="C116" t="s">
-        <v>297</v>
-      </c>
-      <c r="D116">
-        <v>74</v>
-      </c>
-      <c r="E116">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A117" t="s">
-        <v>298</v>
-      </c>
-      <c r="B117" t="s">
-        <v>299</v>
-      </c>
-      <c r="C117" t="s">
-        <v>298</v>
-      </c>
-      <c r="D117">
-        <v>73</v>
-      </c>
-      <c r="E117">
-        <v>6.8</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A118" t="s">
-        <v>300</v>
-      </c>
-      <c r="B118" t="s">
-        <v>301</v>
-      </c>
-      <c r="C118" t="s">
-        <v>302</v>
-      </c>
-      <c r="D118">
-        <v>73</v>
-      </c>
-      <c r="E118">
-        <v>42.5</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A119" t="s">
-        <v>303</v>
-      </c>
-      <c r="B119" t="s">
-        <v>304</v>
-      </c>
-      <c r="C119" t="s">
-        <v>305</v>
-      </c>
-      <c r="D119">
-        <v>73</v>
-      </c>
-      <c r="E119">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A120" t="s">
-        <v>306</v>
-      </c>
-      <c r="B120" t="s">
-        <v>307</v>
-      </c>
-      <c r="C120" t="s">
-        <v>306</v>
-      </c>
-      <c r="D120">
-        <v>72</v>
-      </c>
-      <c r="E120">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A121" t="s">
-        <v>308</v>
-      </c>
-      <c r="B121" t="s">
-        <v>309</v>
-      </c>
-      <c r="C121" t="s">
-        <v>308</v>
-      </c>
-      <c r="D121">
-        <v>71</v>
-      </c>
-      <c r="E121">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A122" t="s">
-        <v>310</v>
-      </c>
-      <c r="B122" t="s">
-        <v>311</v>
-      </c>
-      <c r="C122" t="s">
-        <v>310</v>
-      </c>
-      <c r="D122">
-        <v>71</v>
-      </c>
-      <c r="E122">
-        <v>5.6</v>
-      </c>
-    </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A123" t="s">
-        <v>312</v>
-      </c>
-      <c r="B123" t="s">
-        <v>313</v>
-      </c>
-      <c r="C123" t="s">
-        <v>314</v>
-      </c>
-      <c r="D123">
-        <v>71</v>
-      </c>
-      <c r="E123">
-        <v>60.6</v>
-      </c>
-      <c r="F123" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A124" t="s">
-        <v>315</v>
-      </c>
-      <c r="B124" t="s">
-        <v>316</v>
-      </c>
-      <c r="C124" t="s">
-        <v>315</v>
-      </c>
-      <c r="D124">
-        <v>70</v>
-      </c>
-      <c r="E124">
-        <v>2.9</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A125" t="s">
-        <v>317</v>
-      </c>
-      <c r="B125" t="s">
-        <v>318</v>
-      </c>
-      <c r="C125" t="s">
-        <v>317</v>
-      </c>
-      <c r="D125">
+      <c r="E160">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>323</v>
+      </c>
+      <c r="B161" t="s">
+        <v>324</v>
+      </c>
+      <c r="C161" t="s">
+        <v>323</v>
+      </c>
+      <c r="D161">
         <v>69</v>
       </c>
-      <c r="E125">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A126" t="s">
-        <v>319</v>
-      </c>
-      <c r="B126" t="s">
-        <v>320</v>
-      </c>
-      <c r="C126" t="s">
-        <v>319</v>
-      </c>
-      <c r="D126">
-        <v>69</v>
-      </c>
-      <c r="E126">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A127" t="s">
-        <v>321</v>
-      </c>
-      <c r="B127" t="s">
-        <v>322</v>
-      </c>
-      <c r="C127" t="s">
-        <v>321</v>
-      </c>
-      <c r="D127">
-        <v>69</v>
-      </c>
-      <c r="E127">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A128" t="s">
-        <v>323</v>
-      </c>
-      <c r="B128" t="s">
-        <v>324</v>
-      </c>
-      <c r="C128" t="s">
-        <v>323</v>
-      </c>
-      <c r="D128">
-        <v>69</v>
-      </c>
-      <c r="E128">
+      <c r="E161">
         <v>34.799999999999997</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A129" t="s">
+    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>375</v>
+      </c>
+      <c r="B162" t="s">
+        <v>376</v>
+      </c>
+      <c r="C162" t="s">
+        <v>375</v>
+      </c>
+      <c r="D162">
+        <v>60</v>
+      </c>
+      <c r="E162">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>341</v>
+      </c>
+      <c r="B163" t="s">
+        <v>342</v>
+      </c>
+      <c r="C163" t="s">
+        <v>341</v>
+      </c>
+      <c r="D163">
+        <v>66</v>
+      </c>
+      <c r="E163">
+        <v>36.4</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>366</v>
+      </c>
+      <c r="B164" t="s">
+        <v>367</v>
+      </c>
+      <c r="C164" t="s">
+        <v>366</v>
+      </c>
+      <c r="D164">
+        <v>62</v>
+      </c>
+      <c r="E164">
+        <v>41.9</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>208</v>
+      </c>
+      <c r="B165" t="s">
+        <v>209</v>
+      </c>
+      <c r="C165" t="s">
+        <v>208</v>
+      </c>
+      <c r="D165">
+        <v>132</v>
+      </c>
+      <c r="E165">
+        <v>37.9</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>466</v>
+      </c>
+      <c r="B166" t="s">
+        <v>467</v>
+      </c>
+      <c r="C166" t="s">
+        <v>468</v>
+      </c>
+      <c r="D166">
+        <v>38</v>
+      </c>
+      <c r="E166">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>333</v>
+      </c>
+      <c r="B167" t="s">
+        <v>334</v>
+      </c>
+      <c r="C167" t="s">
+        <v>335</v>
+      </c>
+      <c r="D167">
+        <v>66</v>
+      </c>
+      <c r="E167">
+        <v>40.9</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>338</v>
+      </c>
+      <c r="B168" t="s">
+        <v>339</v>
+      </c>
+      <c r="C168" t="s">
+        <v>340</v>
+      </c>
+      <c r="D168">
+        <v>66</v>
+      </c>
+      <c r="E168">
+        <v>37.9</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>216</v>
+      </c>
+      <c r="B169" t="s">
+        <v>217</v>
+      </c>
+      <c r="C169" t="s">
+        <v>216</v>
+      </c>
+      <c r="D169">
+        <v>124</v>
+      </c>
+      <c r="E169">
+        <v>40.299999999999997</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>212</v>
+      </c>
+      <c r="B170" t="s">
+        <v>213</v>
+      </c>
+      <c r="C170" t="s">
+        <v>212</v>
+      </c>
+      <c r="D170">
+        <v>126</v>
+      </c>
+      <c r="E170">
+        <v>39.700000000000003</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>201</v>
+      </c>
+      <c r="B171" t="s">
+        <v>202</v>
+      </c>
+      <c r="C171" t="s">
+        <v>203</v>
+      </c>
+      <c r="D171">
+        <v>135</v>
+      </c>
+      <c r="E171">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
         <v>325</v>
       </c>
-      <c r="B129" t="s">
+      <c r="B172" t="s">
         <v>326</v>
       </c>
-      <c r="C129" t="s">
+      <c r="C172" t="s">
         <v>327</v>
       </c>
-      <c r="D129">
+      <c r="D172">
         <v>67</v>
       </c>
-      <c r="E129">
+      <c r="E172">
         <v>40.299999999999997</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A130" t="s">
-        <v>328</v>
-      </c>
-      <c r="B130" t="s">
-        <v>329</v>
-      </c>
-      <c r="C130" t="s">
-        <v>328</v>
-      </c>
-      <c r="D130">
-        <v>67</v>
-      </c>
-      <c r="E130">
-        <v>25.4</v>
-      </c>
-    </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A131" t="s">
-        <v>330</v>
-      </c>
-      <c r="B131" t="s">
-        <v>331</v>
-      </c>
-      <c r="C131" t="s">
-        <v>332</v>
-      </c>
-      <c r="D131">
-        <v>66</v>
-      </c>
-      <c r="E131">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A132" t="s">
-        <v>333</v>
-      </c>
-      <c r="B132" t="s">
-        <v>334</v>
-      </c>
-      <c r="C132" t="s">
-        <v>335</v>
-      </c>
-      <c r="D132">
-        <v>66</v>
-      </c>
-      <c r="E132">
-        <v>40.9</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A133" t="s">
-        <v>336</v>
-      </c>
-      <c r="B133" t="s">
-        <v>337</v>
-      </c>
-      <c r="C133" t="s">
-        <v>336</v>
-      </c>
-      <c r="D133">
-        <v>66</v>
-      </c>
-      <c r="E133">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A134" t="s">
-        <v>338</v>
-      </c>
-      <c r="B134" t="s">
-        <v>339</v>
-      </c>
-      <c r="C134" t="s">
-        <v>340</v>
-      </c>
-      <c r="D134">
-        <v>66</v>
-      </c>
-      <c r="E134">
-        <v>37.9</v>
-      </c>
-    </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A135" t="s">
-        <v>341</v>
-      </c>
-      <c r="B135" t="s">
-        <v>342</v>
-      </c>
-      <c r="C135" t="s">
-        <v>341</v>
-      </c>
-      <c r="D135">
-        <v>66</v>
-      </c>
-      <c r="E135">
-        <v>36.4</v>
-      </c>
-    </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A136" t="s">
-        <v>343</v>
-      </c>
-      <c r="B136" t="s">
-        <v>344</v>
-      </c>
-      <c r="C136" t="s">
-        <v>343</v>
-      </c>
-      <c r="D136">
+    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>469</v>
+      </c>
+      <c r="B173" t="s">
+        <v>470</v>
+      </c>
+      <c r="C173" t="s">
+        <v>471</v>
+      </c>
+      <c r="D173">
+        <v>37</v>
+      </c>
+      <c r="E173">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>354</v>
+      </c>
+      <c r="B174" t="s">
+        <v>355</v>
+      </c>
+      <c r="C174" t="s">
+        <v>356</v>
+      </c>
+      <c r="D174">
+        <v>63</v>
+      </c>
+      <c r="E174">
+        <v>42.9</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>347</v>
+      </c>
+      <c r="B175" t="s">
+        <v>348</v>
+      </c>
+      <c r="C175" t="s">
+        <v>349</v>
+      </c>
+      <c r="D175">
         <v>65</v>
       </c>
-      <c r="E136">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A137" t="s">
-        <v>345</v>
-      </c>
-      <c r="B137" t="s">
-        <v>346</v>
-      </c>
-      <c r="C137" t="s">
-        <v>345</v>
-      </c>
-      <c r="D137">
-        <v>65</v>
-      </c>
-      <c r="E137">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A138" t="s">
-        <v>347</v>
-      </c>
-      <c r="B138" t="s">
-        <v>348</v>
-      </c>
-      <c r="C138" t="s">
-        <v>349</v>
-      </c>
-      <c r="D138">
-        <v>65</v>
-      </c>
-      <c r="E138">
+      <c r="E175">
         <v>44.6</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A139" t="s">
-        <v>350</v>
-      </c>
-      <c r="B139" t="s">
-        <v>351</v>
-      </c>
-      <c r="C139" t="s">
-        <v>350</v>
-      </c>
-      <c r="D139">
-        <v>64</v>
-      </c>
-      <c r="E139">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A140" t="s">
-        <v>352</v>
-      </c>
-      <c r="B140" t="s">
-        <v>353</v>
-      </c>
-      <c r="C140" t="s">
-        <v>352</v>
-      </c>
-      <c r="D140">
-        <v>63</v>
-      </c>
-      <c r="E140">
-        <v>3.2</v>
-      </c>
-    </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A141" t="s">
-        <v>354</v>
-      </c>
-      <c r="B141" t="s">
-        <v>355</v>
-      </c>
-      <c r="C141" t="s">
-        <v>356</v>
-      </c>
-      <c r="D141">
-        <v>63</v>
-      </c>
-      <c r="E141">
-        <v>42.9</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A142" t="s">
-        <v>357</v>
-      </c>
-      <c r="B142" t="s">
-        <v>358</v>
-      </c>
-      <c r="C142" t="s">
-        <v>357</v>
-      </c>
-      <c r="D142">
-        <v>63</v>
-      </c>
-      <c r="E142">
-        <v>4.8</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A143" t="s">
-        <v>359</v>
-      </c>
-      <c r="B143" t="s">
-        <v>360</v>
-      </c>
-      <c r="C143" t="s">
-        <v>361</v>
-      </c>
-      <c r="D143">
-        <v>63</v>
-      </c>
-      <c r="E143">
-        <v>17.5</v>
-      </c>
-    </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A144" t="s">
-        <v>362</v>
-      </c>
-      <c r="B144" t="s">
-        <v>363</v>
-      </c>
-      <c r="C144" t="s">
-        <v>362</v>
-      </c>
-      <c r="D144">
-        <v>63</v>
-      </c>
-      <c r="E144">
-        <v>19</v>
-      </c>
-      <c r="F144" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A145" t="s">
-        <v>364</v>
-      </c>
-      <c r="B145" t="s">
-        <v>365</v>
-      </c>
-      <c r="C145" t="s">
-        <v>364</v>
-      </c>
-      <c r="D145">
-        <v>63</v>
-      </c>
-      <c r="E145">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A146" t="s">
-        <v>366</v>
-      </c>
-      <c r="B146" t="s">
-        <v>367</v>
-      </c>
-      <c r="C146" t="s">
-        <v>366</v>
-      </c>
-      <c r="D146">
-        <v>62</v>
-      </c>
-      <c r="E146">
-        <v>41.9</v>
-      </c>
-    </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A147" t="s">
-        <v>368</v>
-      </c>
-      <c r="B147" t="s">
-        <v>369</v>
-      </c>
-      <c r="C147" t="s">
-        <v>370</v>
-      </c>
-      <c r="D147">
-        <v>62</v>
-      </c>
-      <c r="E147">
-        <v>100</v>
-      </c>
-      <c r="F147" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A148" t="s">
-        <v>371</v>
-      </c>
-      <c r="B148" t="s">
-        <v>372</v>
-      </c>
-      <c r="C148" t="s">
-        <v>371</v>
-      </c>
-      <c r="D148">
-        <v>61</v>
-      </c>
-      <c r="E148">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A149" t="s">
-        <v>373</v>
-      </c>
-      <c r="B149" t="s">
-        <v>374</v>
-      </c>
-      <c r="C149" t="s">
-        <v>373</v>
-      </c>
-      <c r="D149">
-        <v>60</v>
-      </c>
-      <c r="E149">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A150" t="s">
-        <v>375</v>
-      </c>
-      <c r="B150" t="s">
-        <v>376</v>
-      </c>
-      <c r="C150" t="s">
-        <v>375</v>
-      </c>
-      <c r="D150">
-        <v>60</v>
-      </c>
-      <c r="E150">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A151" t="s">
-        <v>377</v>
-      </c>
-      <c r="B151" t="s">
-        <v>378</v>
-      </c>
-      <c r="C151" t="s">
-        <v>377</v>
-      </c>
-      <c r="D151">
-        <v>60</v>
-      </c>
-      <c r="E151">
-        <v>1.7</v>
-      </c>
-    </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A152" t="s">
-        <v>379</v>
-      </c>
-      <c r="B152" t="s">
-        <v>380</v>
-      </c>
-      <c r="C152" t="s">
-        <v>379</v>
-      </c>
-      <c r="D152">
-        <v>60</v>
-      </c>
-      <c r="E152">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A153" t="s">
-        <v>381</v>
-      </c>
-      <c r="B153" t="s">
-        <v>382</v>
-      </c>
-      <c r="C153" t="s">
-        <v>381</v>
-      </c>
-      <c r="D153">
-        <v>59</v>
-      </c>
-      <c r="E153">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A154" t="s">
-        <v>383</v>
-      </c>
-      <c r="B154" t="s">
-        <v>384</v>
-      </c>
-      <c r="C154" t="s">
-        <v>385</v>
-      </c>
-      <c r="D154">
-        <v>59</v>
-      </c>
-      <c r="E154">
-        <v>3.4</v>
-      </c>
-    </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A155" t="s">
-        <v>386</v>
-      </c>
-      <c r="B155" t="s">
-        <v>387</v>
-      </c>
-      <c r="C155" t="s">
-        <v>386</v>
-      </c>
-      <c r="D155">
-        <v>58</v>
-      </c>
-      <c r="E155">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A156" t="s">
-        <v>388</v>
-      </c>
-      <c r="B156" t="s">
-        <v>389</v>
-      </c>
-      <c r="C156" t="s">
-        <v>388</v>
-      </c>
-      <c r="D156">
-        <v>57</v>
-      </c>
-      <c r="E156">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A157" t="s">
-        <v>390</v>
-      </c>
-      <c r="B157" t="s">
-        <v>391</v>
-      </c>
-      <c r="C157" t="s">
-        <v>390</v>
-      </c>
-      <c r="D157">
-        <v>57</v>
-      </c>
-      <c r="E157">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A158" t="s">
-        <v>392</v>
-      </c>
-      <c r="B158" t="s">
-        <v>393</v>
-      </c>
-      <c r="C158" t="s">
-        <v>392</v>
-      </c>
-      <c r="D158">
-        <v>57</v>
-      </c>
-      <c r="E158">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A159" t="s">
-        <v>394</v>
-      </c>
-      <c r="B159" t="s">
-        <v>395</v>
-      </c>
-      <c r="C159" t="s">
-        <v>394</v>
-      </c>
-      <c r="D159">
-        <v>57</v>
-      </c>
-      <c r="E159">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A160" t="s">
-        <v>396</v>
-      </c>
-      <c r="B160" t="s">
-        <v>397</v>
-      </c>
-      <c r="C160" t="s">
-        <v>396</v>
-      </c>
-      <c r="D160">
-        <v>57</v>
-      </c>
-      <c r="E160">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A161" t="s">
-        <v>398</v>
-      </c>
-      <c r="B161" t="s">
-        <v>399</v>
-      </c>
-      <c r="C161" t="s">
-        <v>398</v>
-      </c>
-      <c r="D161">
-        <v>56</v>
-      </c>
-      <c r="E161">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A162" t="s">
-        <v>400</v>
-      </c>
-      <c r="B162" t="s">
-        <v>401</v>
-      </c>
-      <c r="C162" t="s">
-        <v>400</v>
-      </c>
-      <c r="D162">
-        <v>56</v>
-      </c>
-      <c r="E162">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A163" t="s">
-        <v>402</v>
-      </c>
-      <c r="B163" t="s">
-        <v>403</v>
-      </c>
-      <c r="C163" t="s">
-        <v>402</v>
-      </c>
-      <c r="D163">
-        <v>56</v>
-      </c>
-      <c r="E163">
-        <v>10.7</v>
-      </c>
-    </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A164" t="s">
-        <v>404</v>
-      </c>
-      <c r="B164" t="s">
-        <v>405</v>
-      </c>
-      <c r="C164" t="s">
-        <v>404</v>
-      </c>
-      <c r="D164">
-        <v>56</v>
-      </c>
-      <c r="E164">
-        <v>32.1</v>
-      </c>
-      <c r="F164" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A165" t="s">
-        <v>406</v>
-      </c>
-      <c r="B165" t="s">
-        <v>407</v>
-      </c>
-      <c r="C165" t="s">
-        <v>406</v>
-      </c>
-      <c r="D165">
-        <v>55</v>
-      </c>
-      <c r="E165">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A166" t="s">
-        <v>408</v>
-      </c>
-      <c r="B166" t="s">
-        <v>409</v>
-      </c>
-      <c r="C166" t="s">
-        <v>408</v>
-      </c>
-      <c r="D166">
-        <v>54</v>
-      </c>
-      <c r="E166">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A167" t="s">
-        <v>410</v>
-      </c>
-      <c r="B167" t="s">
-        <v>411</v>
-      </c>
-      <c r="C167" t="s">
-        <v>410</v>
-      </c>
-      <c r="D167">
-        <v>54</v>
-      </c>
-      <c r="E167">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A168" t="s">
-        <v>412</v>
-      </c>
-      <c r="B168" t="s">
-        <v>413</v>
-      </c>
-      <c r="C168" t="s">
-        <v>412</v>
-      </c>
-      <c r="D168">
-        <v>54</v>
-      </c>
-      <c r="E168">
-        <v>7.4</v>
-      </c>
-    </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A169" t="s">
-        <v>414</v>
-      </c>
-      <c r="B169" t="s">
-        <v>415</v>
-      </c>
-      <c r="C169" t="s">
-        <v>414</v>
-      </c>
-      <c r="D169">
-        <v>54</v>
-      </c>
-      <c r="E169">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A170" t="s">
-        <v>416</v>
-      </c>
-      <c r="B170" t="s">
-        <v>417</v>
-      </c>
-      <c r="C170" t="s">
-        <v>416</v>
-      </c>
-      <c r="D170">
-        <v>53</v>
-      </c>
-      <c r="E170">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A171" t="s">
-        <v>418</v>
-      </c>
-      <c r="B171" t="s">
-        <v>419</v>
-      </c>
-      <c r="C171" t="s">
-        <v>418</v>
-      </c>
-      <c r="D171">
-        <v>53</v>
-      </c>
-      <c r="E171">
-        <v>3.8</v>
-      </c>
-    </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A172" t="s">
-        <v>420</v>
-      </c>
-      <c r="B172" t="s">
-        <v>421</v>
-      </c>
-      <c r="C172" t="s">
-        <v>420</v>
-      </c>
-      <c r="D172">
-        <v>52</v>
-      </c>
-      <c r="E172">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A173" t="s">
-        <v>422</v>
-      </c>
-      <c r="B173" t="s">
-        <v>423</v>
-      </c>
-      <c r="C173" t="s">
-        <v>422</v>
-      </c>
-      <c r="D173">
-        <v>52</v>
-      </c>
-      <c r="E173">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A174" t="s">
-        <v>424</v>
-      </c>
-      <c r="B174" t="s">
-        <v>425</v>
-      </c>
-      <c r="C174" t="s">
-        <v>424</v>
-      </c>
-      <c r="D174">
-        <v>52</v>
-      </c>
-      <c r="E174">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A175" t="s">
-        <v>426</v>
-      </c>
-      <c r="B175" t="s">
-        <v>427</v>
-      </c>
-      <c r="C175" t="s">
-        <v>426</v>
-      </c>
-      <c r="D175">
-        <v>51</v>
-      </c>
-      <c r="E175">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>428</v>
+        <v>452</v>
       </c>
       <c r="B176" t="s">
-        <v>429</v>
+        <v>453</v>
       </c>
       <c r="C176" t="s">
-        <v>428</v>
+        <v>452</v>
       </c>
       <c r="D176">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="E176">
-        <v>6</v>
+        <v>11.6</v>
       </c>
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>430</v>
+        <v>442</v>
       </c>
       <c r="B177" t="s">
-        <v>431</v>
+        <v>443</v>
       </c>
       <c r="C177" t="s">
-        <v>430</v>
+        <v>442</v>
       </c>
       <c r="D177">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E177">
-        <v>42</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>432</v>
+        <v>404</v>
       </c>
       <c r="B178" t="s">
-        <v>433</v>
+        <v>405</v>
       </c>
       <c r="C178" t="s">
-        <v>432</v>
+        <v>404</v>
       </c>
       <c r="D178">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="E178">
-        <v>34.700000000000003</v>
+        <v>32.1</v>
       </c>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>434</v>
+        <v>377</v>
       </c>
       <c r="B179" t="s">
-        <v>435</v>
+        <v>378</v>
       </c>
       <c r="C179" t="s">
-        <v>434</v>
+        <v>377</v>
       </c>
       <c r="D179">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="E179">
-        <v>0</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>436</v>
+        <v>396</v>
       </c>
       <c r="B180" t="s">
-        <v>437</v>
+        <v>397</v>
       </c>
       <c r="C180" t="s">
-        <v>436</v>
+        <v>396</v>
       </c>
       <c r="D180">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="E180">
         <v>0</v>
@@ -5270,16 +5270,16 @@
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>438</v>
+        <v>481</v>
       </c>
       <c r="B181" t="s">
-        <v>439</v>
+        <v>482</v>
       </c>
       <c r="C181" t="s">
-        <v>438</v>
+        <v>481</v>
       </c>
       <c r="D181">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="E181">
         <v>0</v>
@@ -5287,84 +5287,84 @@
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>440</v>
+        <v>488</v>
       </c>
       <c r="B182" t="s">
-        <v>441</v>
+        <v>489</v>
       </c>
       <c r="C182" t="s">
-        <v>440</v>
+        <v>488</v>
       </c>
       <c r="D182">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="E182">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>442</v>
+        <v>490</v>
       </c>
       <c r="B183" t="s">
-        <v>443</v>
+        <v>491</v>
       </c>
       <c r="C183" t="s">
-        <v>442</v>
+        <v>490</v>
       </c>
       <c r="D183">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="E183">
-        <v>6.4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>444</v>
+        <v>269</v>
       </c>
       <c r="B184" t="s">
-        <v>445</v>
+        <v>270</v>
       </c>
       <c r="C184" t="s">
-        <v>444</v>
+        <v>269</v>
       </c>
       <c r="D184">
-        <v>47</v>
+        <v>79</v>
       </c>
       <c r="E184">
-        <v>17</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>446</v>
+        <v>271</v>
       </c>
       <c r="B185" t="s">
-        <v>447</v>
+        <v>272</v>
       </c>
       <c r="C185" t="s">
-        <v>446</v>
+        <v>271</v>
       </c>
       <c r="D185">
-        <v>46</v>
+        <v>79</v>
       </c>
       <c r="E185">
-        <v>0</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>448</v>
+        <v>456</v>
       </c>
       <c r="B186" t="s">
-        <v>449</v>
+        <v>457</v>
       </c>
       <c r="C186" t="s">
-        <v>448</v>
+        <v>456</v>
       </c>
       <c r="D186">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E186">
         <v>0</v>
@@ -5372,50 +5372,50 @@
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>450</v>
+        <v>218</v>
       </c>
       <c r="B187" t="s">
-        <v>451</v>
+        <v>219</v>
       </c>
       <c r="C187" t="s">
-        <v>450</v>
+        <v>218</v>
       </c>
       <c r="D187">
-        <v>45</v>
+        <v>120</v>
       </c>
       <c r="E187">
-        <v>0</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>452</v>
+        <v>432</v>
       </c>
       <c r="B188" t="s">
-        <v>453</v>
+        <v>433</v>
       </c>
       <c r="C188" t="s">
-        <v>452</v>
+        <v>432</v>
       </c>
       <c r="D188">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="E188">
-        <v>11.6</v>
+        <v>34.700000000000003</v>
       </c>
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>454</v>
+        <v>126</v>
       </c>
       <c r="B189" t="s">
-        <v>455</v>
+        <v>127</v>
       </c>
       <c r="C189" t="s">
-        <v>454</v>
+        <v>126</v>
       </c>
       <c r="D189">
-        <v>41</v>
+        <v>202</v>
       </c>
       <c r="E189">
         <v>0</v>
@@ -5423,101 +5423,101 @@
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>456</v>
+        <v>357</v>
       </c>
       <c r="B190" t="s">
-        <v>457</v>
+        <v>358</v>
       </c>
       <c r="C190" t="s">
-        <v>456</v>
+        <v>357</v>
       </c>
       <c r="D190">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="E190">
-        <v>0</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>458</v>
+        <v>503</v>
       </c>
       <c r="B191" t="s">
-        <v>459</v>
+        <v>504</v>
       </c>
       <c r="C191" t="s">
-        <v>458</v>
+        <v>503</v>
       </c>
       <c r="D191">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="E191">
-        <v>0</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>460</v>
+        <v>284</v>
       </c>
       <c r="B192" t="s">
-        <v>461</v>
+        <v>285</v>
       </c>
       <c r="C192" t="s">
-        <v>460</v>
+        <v>286</v>
       </c>
       <c r="D192">
-        <v>39</v>
+        <v>75</v>
       </c>
       <c r="E192">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>462</v>
+        <v>511</v>
       </c>
       <c r="B193" t="s">
-        <v>463</v>
+        <v>512</v>
       </c>
       <c r="C193" t="s">
-        <v>462</v>
+        <v>511</v>
       </c>
       <c r="D193">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="E193">
-        <v>0</v>
+        <v>26.9</v>
       </c>
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>464</v>
+        <v>300</v>
       </c>
       <c r="B194" t="s">
-        <v>465</v>
+        <v>301</v>
       </c>
       <c r="C194" t="s">
-        <v>464</v>
+        <v>302</v>
       </c>
       <c r="D194">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="E194">
-        <v>0</v>
+        <v>42.5</v>
       </c>
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>466</v>
+        <v>513</v>
       </c>
       <c r="B195" t="s">
-        <v>467</v>
+        <v>514</v>
       </c>
       <c r="C195" t="s">
-        <v>468</v>
+        <v>513</v>
       </c>
       <c r="D195">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="E195">
         <v>0</v>
@@ -5525,16 +5525,16 @@
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>469</v>
+        <v>295</v>
       </c>
       <c r="B196" t="s">
-        <v>470</v>
+        <v>296</v>
       </c>
       <c r="C196" t="s">
-        <v>471</v>
+        <v>297</v>
       </c>
       <c r="D196">
-        <v>37</v>
+        <v>74</v>
       </c>
       <c r="E196">
         <v>0</v>
@@ -5542,50 +5542,50 @@
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>472</v>
+        <v>515</v>
       </c>
       <c r="B197" t="s">
-        <v>473</v>
+        <v>516</v>
       </c>
       <c r="C197" t="s">
-        <v>474</v>
+        <v>515</v>
       </c>
       <c r="D197">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="E197">
-        <v>0</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>475</v>
+        <v>303</v>
       </c>
       <c r="B198" t="s">
-        <v>476</v>
+        <v>304</v>
       </c>
       <c r="C198" t="s">
-        <v>475</v>
+        <v>305</v>
       </c>
       <c r="D198">
-        <v>36</v>
+        <v>73</v>
       </c>
       <c r="E198">
-        <v>2.8</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>477</v>
+        <v>276</v>
       </c>
       <c r="B199" t="s">
-        <v>478</v>
+        <v>277</v>
       </c>
       <c r="C199" t="s">
-        <v>477</v>
+        <v>276</v>
       </c>
       <c r="D199">
-        <v>35</v>
+        <v>77</v>
       </c>
       <c r="E199">
         <v>0</v>
@@ -5593,16 +5593,16 @@
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>479</v>
+        <v>118</v>
       </c>
       <c r="B200" t="s">
-        <v>480</v>
+        <v>119</v>
       </c>
       <c r="C200" t="s">
-        <v>479</v>
+        <v>120</v>
       </c>
       <c r="D200">
-        <v>35</v>
+        <v>218</v>
       </c>
       <c r="E200">
         <v>0</v>
@@ -5610,16 +5610,16 @@
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>481</v>
+        <v>539</v>
       </c>
       <c r="B201" t="s">
-        <v>482</v>
+        <v>540</v>
       </c>
       <c r="C201" t="s">
-        <v>481</v>
+        <v>539</v>
       </c>
       <c r="D201">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="E201">
         <v>0</v>
@@ -5627,16 +5627,16 @@
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>483</v>
+        <v>525</v>
       </c>
       <c r="B202" t="s">
-        <v>484</v>
+        <v>526</v>
       </c>
       <c r="C202" t="s">
-        <v>483</v>
+        <v>525</v>
       </c>
       <c r="D202">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="E202">
         <v>0</v>
@@ -5644,67 +5644,67 @@
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>485</v>
+        <v>541</v>
       </c>
       <c r="B203" t="s">
-        <v>486</v>
+        <v>542</v>
       </c>
       <c r="C203" t="s">
-        <v>487</v>
+        <v>541</v>
       </c>
       <c r="D203">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="E203">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>488</v>
+        <v>533</v>
       </c>
       <c r="B204" t="s">
-        <v>489</v>
+        <v>534</v>
       </c>
       <c r="C204" t="s">
-        <v>488</v>
+        <v>533</v>
       </c>
       <c r="D204">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="E204">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>490</v>
+        <v>537</v>
       </c>
       <c r="B205" t="s">
-        <v>491</v>
+        <v>538</v>
       </c>
       <c r="C205" t="s">
-        <v>490</v>
+        <v>537</v>
       </c>
       <c r="D205">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="E205">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>492</v>
+        <v>472</v>
       </c>
       <c r="B206" t="s">
-        <v>493</v>
+        <v>473</v>
       </c>
       <c r="C206" t="s">
-        <v>494</v>
+        <v>474</v>
       </c>
       <c r="D206">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="E206">
         <v>0</v>
@@ -5712,33 +5712,33 @@
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>495</v>
+        <v>545</v>
       </c>
       <c r="B207" t="s">
-        <v>496</v>
+        <v>546</v>
       </c>
       <c r="C207" t="s">
-        <v>495</v>
+        <v>545</v>
       </c>
       <c r="D207">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="E207">
-        <v>3.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>497</v>
+        <v>547</v>
       </c>
       <c r="B208" t="s">
-        <v>498</v>
+        <v>548</v>
       </c>
       <c r="C208" t="s">
-        <v>497</v>
+        <v>547</v>
       </c>
       <c r="D208">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="E208">
         <v>0</v>
@@ -5746,16 +5746,16 @@
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>499</v>
+        <v>549</v>
       </c>
       <c r="B209" t="s">
-        <v>500</v>
+        <v>550</v>
       </c>
       <c r="C209" t="s">
-        <v>499</v>
+        <v>549</v>
       </c>
       <c r="D209">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="E209">
         <v>0</v>
@@ -5763,16 +5763,16 @@
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>501</v>
+        <v>551</v>
       </c>
       <c r="B210" t="s">
-        <v>502</v>
+        <v>552</v>
       </c>
       <c r="C210" t="s">
-        <v>501</v>
+        <v>551</v>
       </c>
       <c r="D210">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="E210">
         <v>0</v>
@@ -5780,84 +5780,84 @@
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>503</v>
+        <v>553</v>
       </c>
       <c r="B211" t="s">
-        <v>504</v>
+        <v>554</v>
       </c>
       <c r="C211" t="s">
-        <v>503</v>
+        <v>553</v>
       </c>
       <c r="D211">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="E211">
-        <v>7.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>505</v>
+        <v>527</v>
       </c>
       <c r="B212" t="s">
-        <v>506</v>
+        <v>528</v>
       </c>
       <c r="C212" t="s">
-        <v>507</v>
+        <v>527</v>
       </c>
       <c r="D212">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="E212">
-        <v>33.299999999999997</v>
+        <v>0</v>
       </c>
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>508</v>
+        <v>522</v>
       </c>
       <c r="B213" t="s">
-        <v>509</v>
+        <v>523</v>
       </c>
       <c r="C213" t="s">
-        <v>510</v>
+        <v>524</v>
       </c>
       <c r="D213">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="E213">
-        <v>7.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>511</v>
+        <v>280</v>
       </c>
       <c r="B214" t="s">
-        <v>512</v>
+        <v>281</v>
       </c>
       <c r="C214" t="s">
-        <v>511</v>
+        <v>280</v>
       </c>
       <c r="D214">
-        <v>26</v>
+        <v>76</v>
       </c>
       <c r="E214">
-        <v>26.9</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>513</v>
+        <v>238</v>
       </c>
       <c r="B215" t="s">
-        <v>514</v>
+        <v>239</v>
       </c>
       <c r="C215" t="s">
-        <v>513</v>
+        <v>240</v>
       </c>
       <c r="D215">
-        <v>26</v>
+        <v>99</v>
       </c>
       <c r="E215">
         <v>0</v>
@@ -5865,84 +5865,84 @@
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>515</v>
+        <v>424</v>
       </c>
       <c r="B216" t="s">
-        <v>516</v>
+        <v>425</v>
       </c>
       <c r="C216" t="s">
-        <v>515</v>
+        <v>424</v>
       </c>
       <c r="D216">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="E216">
-        <v>7.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="217" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>517</v>
+        <v>505</v>
       </c>
       <c r="B217" t="s">
-        <v>518</v>
+        <v>506</v>
       </c>
       <c r="C217" t="s">
-        <v>519</v>
+        <v>507</v>
       </c>
       <c r="D217">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E217">
-        <v>0</v>
+        <v>33.299999999999997</v>
       </c>
     </row>
     <row r="218" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>520</v>
+        <v>261</v>
       </c>
       <c r="B218" t="s">
-        <v>521</v>
+        <v>262</v>
       </c>
       <c r="C218" t="s">
-        <v>520</v>
+        <v>263</v>
       </c>
       <c r="D218">
-        <v>23</v>
+        <v>80</v>
       </c>
       <c r="E218">
-        <v>0</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>522</v>
+        <v>430</v>
       </c>
       <c r="B219" t="s">
-        <v>523</v>
+        <v>431</v>
       </c>
       <c r="C219" t="s">
-        <v>524</v>
+        <v>430</v>
       </c>
       <c r="D219">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="E219">
-        <v>0</v>
+        <v>42</v>
       </c>
     </row>
     <row r="220" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>525</v>
+        <v>273</v>
       </c>
       <c r="B220" t="s">
-        <v>526</v>
+        <v>274</v>
       </c>
       <c r="C220" t="s">
-        <v>525</v>
+        <v>275</v>
       </c>
       <c r="D220">
-        <v>18</v>
+        <v>78</v>
       </c>
       <c r="E220">
         <v>0</v>
@@ -5950,33 +5950,33 @@
     </row>
     <row r="221" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>527</v>
+        <v>428</v>
       </c>
       <c r="B221" t="s">
-        <v>528</v>
+        <v>429</v>
       </c>
       <c r="C221" t="s">
-        <v>527</v>
+        <v>428</v>
       </c>
       <c r="D221">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="E221">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="222" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>529</v>
+        <v>517</v>
       </c>
       <c r="B222" t="s">
-        <v>530</v>
+        <v>518</v>
       </c>
       <c r="C222" t="s">
-        <v>529</v>
+        <v>519</v>
       </c>
       <c r="D222">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="E222">
         <v>0</v>
@@ -5984,50 +5984,50 @@
     </row>
     <row r="223" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>531</v>
+        <v>444</v>
       </c>
       <c r="B223" t="s">
-        <v>532</v>
+        <v>445</v>
       </c>
       <c r="C223" t="s">
-        <v>531</v>
+        <v>444</v>
       </c>
       <c r="D223">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="E223">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="224" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>533</v>
+        <v>115</v>
       </c>
       <c r="B224" t="s">
-        <v>534</v>
+        <v>116</v>
       </c>
       <c r="C224" t="s">
-        <v>533</v>
+        <v>117</v>
       </c>
       <c r="D224">
-        <v>14</v>
+        <v>225</v>
       </c>
       <c r="E224">
-        <v>0</v>
+        <v>20.399999999999999</v>
       </c>
     </row>
     <row r="225" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>535</v>
+        <v>364</v>
       </c>
       <c r="B225" t="s">
-        <v>536</v>
+        <v>365</v>
       </c>
       <c r="C225" t="s">
-        <v>535</v>
+        <v>364</v>
       </c>
       <c r="D225">
-        <v>13</v>
+        <v>63</v>
       </c>
       <c r="E225">
         <v>0</v>
@@ -6035,50 +6035,50 @@
     </row>
     <row r="226" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>537</v>
+        <v>359</v>
       </c>
       <c r="B226" t="s">
-        <v>538</v>
+        <v>360</v>
       </c>
       <c r="C226" t="s">
-        <v>537</v>
+        <v>361</v>
       </c>
       <c r="D226">
-        <v>13</v>
+        <v>63</v>
       </c>
       <c r="E226">
-        <v>0</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="227" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>539</v>
+        <v>508</v>
       </c>
       <c r="B227" t="s">
-        <v>540</v>
+        <v>509</v>
       </c>
       <c r="C227" t="s">
-        <v>539</v>
+        <v>510</v>
       </c>
       <c r="D227">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="E227">
-        <v>0</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="228" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>541</v>
+        <v>112</v>
       </c>
       <c r="B228" t="s">
-        <v>542</v>
+        <v>113</v>
       </c>
       <c r="C228" t="s">
-        <v>541</v>
+        <v>114</v>
       </c>
       <c r="D228">
-        <v>12</v>
+        <v>227</v>
       </c>
       <c r="E228">
         <v>0</v>
@@ -6086,16 +6086,16 @@
     </row>
     <row r="229" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>543</v>
+        <v>555</v>
       </c>
       <c r="B229" t="s">
-        <v>544</v>
+        <v>556</v>
       </c>
       <c r="C229" t="s">
-        <v>543</v>
+        <v>555</v>
       </c>
       <c r="D229">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E229">
         <v>0</v>
@@ -6103,16 +6103,16 @@
     </row>
     <row r="230" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>545</v>
+        <v>434</v>
       </c>
       <c r="B230" t="s">
-        <v>546</v>
+        <v>435</v>
       </c>
       <c r="C230" t="s">
-        <v>545</v>
+        <v>434</v>
       </c>
       <c r="D230">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="E230">
         <v>0</v>
@@ -6120,33 +6120,33 @@
     </row>
     <row r="231" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>547</v>
+        <v>418</v>
       </c>
       <c r="B231" t="s">
-        <v>548</v>
+        <v>419</v>
       </c>
       <c r="C231" t="s">
-        <v>547</v>
+        <v>418</v>
       </c>
       <c r="D231">
-        <v>8</v>
+        <v>53</v>
       </c>
       <c r="E231">
-        <v>0</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="232" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>549</v>
+        <v>414</v>
       </c>
       <c r="B232" t="s">
-        <v>550</v>
+        <v>415</v>
       </c>
       <c r="C232" t="s">
-        <v>549</v>
+        <v>414</v>
       </c>
       <c r="D232">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="E232">
         <v>0</v>
@@ -6154,16 +6154,16 @@
     </row>
     <row r="233" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>551</v>
+        <v>379</v>
       </c>
       <c r="B233" t="s">
-        <v>552</v>
+        <v>380</v>
       </c>
       <c r="C233" t="s">
-        <v>551</v>
+        <v>379</v>
       </c>
       <c r="D233">
-        <v>8</v>
+        <v>60</v>
       </c>
       <c r="E233">
         <v>0</v>
@@ -6171,16 +6171,16 @@
     </row>
     <row r="234" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>553</v>
+        <v>223</v>
       </c>
       <c r="B234" t="s">
-        <v>554</v>
+        <v>224</v>
       </c>
       <c r="C234" t="s">
-        <v>553</v>
+        <v>223</v>
       </c>
       <c r="D234">
-        <v>8</v>
+        <v>116</v>
       </c>
       <c r="E234">
         <v>0</v>
@@ -6188,23 +6188,27 @@
     </row>
     <row r="235" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>555</v>
+        <v>328</v>
       </c>
       <c r="B235" t="s">
-        <v>556</v>
+        <v>329</v>
       </c>
       <c r="C235" t="s">
-        <v>555</v>
+        <v>328</v>
       </c>
       <c r="D235">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="E235">
-        <v>0</v>
+        <v>25.4</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:F1" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F235">
+      <sortCondition ref="F1"/>
+    </sortState>
+  </autoFilter>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" sqref="F2:F235" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"X"</formula1>
